--- a/data/trans_dic/IP31KM16_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM16_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,85; 13,66</t>
+          <t>4,2; 33,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,98; 36,3</t>
+          <t>4,9; 13,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,73; 25,52</t>
+          <t>5,96; 19,47</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,56; 24,11</t>
+          <t>7,24; 15,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,11; 14,66</t>
+          <t>9,01; 18,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,32; 16,7</t>
+          <t>9,22; 15,1</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,31; 13,87</t>
+          <t>9,04; 18,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,49; 17,42</t>
+          <t>7,64; 16,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,69; 14,14</t>
+          <t>9,41; 15,82</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,84; 25,17</t>
+          <t>11,6; 21,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,17; 21,03</t>
+          <t>13,36; 24,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,94; 20,97</t>
+          <t>13,6; 20,77</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,63; 16,39</t>
+          <t>10,31; 16,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,22; 17,57</t>
+          <t>10,92; 15,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,07; 15,43</t>
+          <t>11,13; 15,0</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9641</t>
+          <t>14491</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17625</t>
+          <t>10084</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27265</t>
+          <t>24575</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5545; 15608</t>
+          <t>5160; 41147</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5439; 49657</t>
+          <t>5817; 16423</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14396; 64075</t>
+          <t>14388; 47027</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>27894</t>
+          <t>25180</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>25817</t>
+          <t>23174</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>53711</t>
+          <t>48354</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19645; 44872</t>
+          <t>16738; 35689</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17597; 36295</t>
+          <t>16266; 32622</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40431; 72436</t>
+          <t>37970; 62184</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17673</t>
+          <t>22117</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22734</t>
+          <t>17293</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40407</t>
+          <t>39409</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9988; 26111</t>
+          <t>15060; 30573</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15542; 31886</t>
+          <t>11848; 25543</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28548; 52502</t>
+          <t>30261; 50860</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>39</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>31010</t>
+          <t>25801</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>27585</t>
+          <t>30069</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58595</t>
+          <t>55870</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22765; 41405</t>
+          <t>19277; 35070</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19800; 37284</t>
+          <t>21915; 39892</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47643; 71689</t>
+          <t>44884; 68568</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>115</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>86218</t>
+          <t>87588</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>93761</t>
+          <t>80621</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>179979</t>
+          <t>168208</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>69400; 107035</t>
+          <t>70780; 112471</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>76109; 130845</t>
+          <t>67528; 96009</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>154711; 215729</t>
+          <t>145236; 195757</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM16_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM16_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que toman golosinas o caramelos varias veces al día (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>11,79%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8,5%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10,18%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>4,2; 33,48</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>4,9; 13,85</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5,96; 19,47</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>10,89%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>12,83%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>11,74%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>7,24; 15,43</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>9,01; 18,06</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9,22; 15,1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>13,28%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>11,15%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>12,26%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>9,04; 18,36</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>7,64; 16,48</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>9,41; 15,82</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>15,53%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>18,34%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>16,92%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>11,6; 21,11</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>13,36; 24,33</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>13,6; 20,77</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>12,75%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>13,04%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>12,89%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>10,31; 16,38</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>10,92; 15,53</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>11,13; 15,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.1179124273270441</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.08502940348770685</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.1017635791990337</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>14491</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>10084</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>24575</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.04198926257617191</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.04904590352462976</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.05958029207781915</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>5160; 41147</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5817; 16423</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>14388; 47027</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.3348099899119302</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.1384751458307164</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.1947338867006175</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.1088888548295993</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.1283240680049486</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.1174113793722121</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>25180</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>23174</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>48354</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.07238339510315701</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.09007095323930828</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.09219836897982206</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>16738; 35689</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>16266; 32622</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>37970; 62184</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.1543361671313266</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.1806392607673966</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.1509928347729003</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.1328152523285978</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.1115384819265715</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1225567875942353</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>22117</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>17293</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>39409</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.09043924080558233</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.07641785654135808</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.09410755736833182</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>15060; 30573</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>11848; 25543</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>30261; 50860</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.1835988443370953</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.1647561535050348</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.1581665681835637</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.1552713485511958</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.1833729309926292</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.1692291055783327</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>25801</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>30069</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>55870</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.1160134545512847</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.1336436356295022</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.1359521824729915</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>19277; 35070</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>21915; 39892</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>44884; 68568</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.2110546059651437</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.2432774764330702</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.2076923939264411</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.1275259157882725</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.1304104234553728</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.1288923387306888</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>87588</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>80621</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>168208</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.1030546284068539</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.1092311941514348</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.111289398160339</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>70780; 112471</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>67528; 96009</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>145236; 195757</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.1637551334233364</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.1553020288256364</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.1500016334189465</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que toman golosinas o caramelos varias veces al día (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>14491</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>10084</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>24575</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>5160</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>5817</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>14388</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>41147</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>16423</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>47027</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>25180</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>23174</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>48354</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>16738</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>16266</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>37970</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>35689</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>32622</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>62184</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>22117</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>17293</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>39409</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>15060</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>11848</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>30261</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>30573</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>25543</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>50860</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>25801</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>30069</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>55870</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>19277</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>21915</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>44884</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>35070</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>39892</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>68568</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>115</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>87588</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>80621</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>168208</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>70780</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>67528</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>145236</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>112471</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>96009</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>195757</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>